--- a/artfynd/A 26571-2021 artfynd.xlsx
+++ b/artfynd/A 26571-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119502073</v>
+        <v>119502084</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>91856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581840</v>
+        <v>581885</v>
       </c>
       <c r="R2" t="n">
-        <v>6657716</v>
+        <v>6657778</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,11 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>granlåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119502084</v>
+        <v>119502073</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581885</v>
+        <v>581840</v>
       </c>
       <c r="R3" t="n">
-        <v>6657778</v>
+        <v>6657716</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,6 +863,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
